--- a/data/code-path-supplement.xlsx
+++ b/data/code-path-supplement.xlsx
@@ -27,29 +27,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>1 indicates that the probe was triggered in this test; 0 indicates it was not triggered.</t>
+  </si>
   <si>
     <t>CVEID</t>
   </si>
   <si>
+    <t>pgbench</t>
+  </si>
+  <si>
     <t>nginx</t>
   </si>
   <si>
+    <t>redis</t>
+  </si>
+  <si>
+    <t>memcached</t>
+  </si>
+  <si>
+    <t>iperf</t>
+  </si>
+  <si>
     <t>apache</t>
   </si>
   <si>
-    <t>pgbench</t>
-  </si>
-  <si>
-    <t>redis</t>
-  </si>
-  <si>
-    <t>memcached</t>
-  </si>
-  <si>
-    <t>iperf</t>
-  </si>
-  <si>
     <t>CVE-2017-1000405</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>CVE-2024-1086</t>
+  </si>
+  <si>
+    <t>Summary</t>
   </si>
 </sst>
 </file>
@@ -759,8 +765,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1296,56 +1305,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="18.0277777777778" customWidth="1"/>
+    <col min="6" max="6" width="9.82407407407407" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1385,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1399,10 +1397,10 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1414,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1422,22 +1420,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1635,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1644,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1652,7 +1650,7 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1664,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1675,22 +1673,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1698,22 +1696,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1882,22 +1880,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1905,22 +1903,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1974,22 +1972,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2043,22 +2041,74 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ref="B35:G35" si="0">SUM(B3:B34)</f>
+        <v>25</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
